--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="F33">
         <v>1</v>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11780"/>
+    <workbookView xWindow="-20" yWindow="-120" windowWidth="28840" windowHeight="11930"/>
   </bookViews>
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
@@ -802,7 +802,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>0.5</v>
@@ -1187,7 +1187,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H15">
         <v>0.5</v>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="109">
   <si>
     <t>id</t>
   </si>
@@ -194,9 +194,6 @@
     <t>投石车(三)</t>
   </si>
   <si>
-    <t>Soldier/Soldier12_1</t>
-  </si>
-  <si>
     <t>冲车</t>
   </si>
   <si>
@@ -351,6 +348,14 @@
   </si>
   <si>
     <t>City/Door_qin</t>
+  </si>
+  <si>
+    <t>5,21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier13_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -802,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>0.5</v>
@@ -1108,19 +1113,19 @@
         <v>54</v>
       </c>
       <c r="D13">
+        <v>22</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
         <v>2</v>
-      </c>
-      <c r="E13">
-        <v>5</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
       </c>
       <c r="I13">
         <v>11</v>
@@ -1129,7 +1134,7 @@
         <v>1.5</v>
       </c>
       <c r="K13" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1137,10 +1142,10 @@
         <v>111</v>
       </c>
       <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
         <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1164,7 +1169,7 @@
         <v>1.5</v>
       </c>
       <c r="K14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1175,7 +1180,7 @@
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1187,7 +1192,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>0.5</v>
@@ -1199,7 +1204,7 @@
         <v>1.5</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1210,7 +1215,7 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1234,7 +1239,7 @@
         <v>1.5</v>
       </c>
       <c r="K16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1245,7 +1250,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1269,7 +1274,7 @@
         <v>1.5</v>
       </c>
       <c r="K17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1280,7 +1285,7 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1304,7 +1309,7 @@
         <v>1.5</v>
       </c>
       <c r="K18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1315,7 +1320,7 @@
         <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -1339,7 +1344,7 @@
         <v>1.5</v>
       </c>
       <c r="K19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1350,7 +1355,7 @@
         <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -1374,7 +1379,7 @@
         <v>1.5</v>
       </c>
       <c r="K20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1382,10 +1387,10 @@
         <v>207</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1409,7 +1414,7 @@
         <v>1.5</v>
       </c>
       <c r="K21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1417,25 +1422,25 @@
         <v>1001</v>
       </c>
       <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
         <v>73</v>
       </c>
-      <c r="C22" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22">
-        <v>5</v>
+      <c r="D22" t="s">
+        <v>107</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
         <v>101</v>
@@ -1444,7 +1449,7 @@
         <v>1.5</v>
       </c>
       <c r="K22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1452,10 +1457,10 @@
         <v>1002</v>
       </c>
       <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" t="s">
         <v>76</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
       </c>
       <c r="D23">
         <v>6</v>
@@ -1479,7 +1484,7 @@
         <v>1.5</v>
       </c>
       <c r="K23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1487,10 +1492,10 @@
         <v>1003</v>
       </c>
       <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
         <v>79</v>
-      </c>
-      <c r="C24" t="s">
-        <v>80</v>
       </c>
       <c r="D24">
         <v>7</v>
@@ -1514,7 +1519,7 @@
         <v>1.5</v>
       </c>
       <c r="K24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1522,10 +1527,10 @@
         <v>1004</v>
       </c>
       <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
         <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>83</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -1549,7 +1554,7 @@
         <v>1.5</v>
       </c>
       <c r="K25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1557,10 +1562,10 @@
         <v>1005</v>
       </c>
       <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" t="s">
         <v>85</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
       </c>
       <c r="D26">
         <v>9</v>
@@ -1584,7 +1589,7 @@
         <v>1.5</v>
       </c>
       <c r="K26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1592,10 +1597,10 @@
         <v>2001</v>
       </c>
       <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
         <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>89</v>
       </c>
       <c r="D27">
         <v>10</v>
@@ -1619,7 +1624,7 @@
         <v>1.5</v>
       </c>
       <c r="K27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1627,10 +1632,10 @@
         <v>2002</v>
       </c>
       <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
         <v>91</v>
-      </c>
-      <c r="C28" t="s">
-        <v>92</v>
       </c>
       <c r="D28">
         <v>11</v>
@@ -1654,7 +1659,7 @@
         <v>1.5</v>
       </c>
       <c r="K28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1662,10 +1667,10 @@
         <v>2003</v>
       </c>
       <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" t="s">
         <v>94</v>
-      </c>
-      <c r="C29" t="s">
-        <v>95</v>
       </c>
       <c r="D29">
         <v>12</v>
@@ -1689,7 +1694,7 @@
         <v>1.5</v>
       </c>
       <c r="K29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1697,10 +1702,10 @@
         <v>2004</v>
       </c>
       <c r="B30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" t="s">
         <v>97</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
       </c>
       <c r="D30">
         <v>13</v>
@@ -1724,7 +1729,7 @@
         <v>1.5</v>
       </c>
       <c r="K30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1732,10 +1737,10 @@
         <v>2005</v>
       </c>
       <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" t="s">
         <v>100</v>
-      </c>
-      <c r="C31" t="s">
-        <v>101</v>
       </c>
       <c r="D31">
         <v>14</v>
@@ -1759,7 +1764,7 @@
         <v>1.5</v>
       </c>
       <c r="K31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1767,10 +1772,10 @@
         <v>10001</v>
       </c>
       <c r="B32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" t="s">
         <v>103</v>
-      </c>
-      <c r="C32" t="s">
-        <v>104</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1794,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1802,10 +1807,10 @@
         <v>20001</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1829,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="114">
   <si>
     <t>id</t>
   </si>
@@ -355,6 +355,26 @@
   </si>
   <si>
     <t>Soldier/Soldier13_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>myLayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignoreLayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忽视层</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -671,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -682,7 +702,7 @@
     <col min="11" max="11" width="57.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -716,8 +736,14 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" t="s">
+        <v>109</v>
+      </c>
+      <c r="M1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -751,8 +777,14 @@
       <c r="K2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>111</v>
+      </c>
+      <c r="M2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -786,8 +818,14 @@
       <c r="K3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>101</v>
       </c>
@@ -821,8 +859,14 @@
       <c r="K4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>102</v>
       </c>
@@ -856,8 +900,14 @@
       <c r="K5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>103</v>
       </c>
@@ -891,8 +941,14 @@
       <c r="K6" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>104</v>
       </c>
@@ -926,8 +982,14 @@
       <c r="K7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>105</v>
       </c>
@@ -961,8 +1023,14 @@
       <c r="K8" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>106</v>
       </c>
@@ -996,8 +1064,14 @@
       <c r="K9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>107</v>
       </c>
@@ -1031,8 +1105,14 @@
       <c r="K10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>108</v>
       </c>
@@ -1066,8 +1146,14 @@
       <c r="K11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>109</v>
       </c>
@@ -1101,8 +1187,14 @@
       <c r="K12" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>110</v>
       </c>
@@ -1136,8 +1228,14 @@
       <c r="K13" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>111</v>
       </c>
@@ -1171,8 +1269,14 @@
       <c r="K14" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15">
         <v>201</v>
       </c>
@@ -1206,8 +1310,14 @@
       <c r="K15" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16">
         <v>202</v>
       </c>
@@ -1241,8 +1351,14 @@
       <c r="K16" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17">
         <v>203</v>
       </c>
@@ -1276,8 +1392,14 @@
       <c r="K17" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18">
         <v>204</v>
       </c>
@@ -1311,8 +1433,14 @@
       <c r="K18" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19">
         <v>205</v>
       </c>
@@ -1346,8 +1474,14 @@
       <c r="K19" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20">
         <v>206</v>
       </c>
@@ -1381,8 +1515,14 @@
       <c r="K20" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21">
         <v>207</v>
       </c>
@@ -1416,8 +1556,14 @@
       <c r="K21" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22">
         <v>1001</v>
       </c>
@@ -1451,8 +1597,14 @@
       <c r="K22" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22">
+        <v>3</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23">
         <v>1002</v>
       </c>
@@ -1486,8 +1638,14 @@
       <c r="K23" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23">
+        <v>3</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24">
         <v>1003</v>
       </c>
@@ -1521,8 +1679,14 @@
       <c r="K24" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24">
+        <v>3</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25">
         <v>1004</v>
       </c>
@@ -1556,8 +1720,14 @@
       <c r="K25" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25">
+        <v>3</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26">
         <v>1005</v>
       </c>
@@ -1591,8 +1761,14 @@
       <c r="K26" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26">
+        <v>3</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27">
         <v>2001</v>
       </c>
@@ -1626,8 +1802,14 @@
       <c r="K27" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="L27">
+        <v>4</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28">
         <v>2002</v>
       </c>
@@ -1661,8 +1843,14 @@
       <c r="K28" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28">
+        <v>4</v>
+      </c>
+      <c r="M28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29">
         <v>2003</v>
       </c>
@@ -1696,8 +1884,14 @@
       <c r="K29" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29">
+        <v>4</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30">
         <v>2004</v>
       </c>
@@ -1731,8 +1925,14 @@
       <c r="K30" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30">
+        <v>4</v>
+      </c>
+      <c r="M30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31">
         <v>2005</v>
       </c>
@@ -1766,8 +1966,14 @@
       <c r="K31" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31">
+        <v>4</v>
+      </c>
+      <c r="M31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32">
         <v>10001</v>
       </c>
@@ -1801,8 +2007,14 @@
       <c r="K32" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33">
         <v>20001</v>
       </c>
@@ -1835,6 +2047,12 @@
       </c>
       <c r="K33" t="s">
         <v>106</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="120">
   <si>
     <t>id</t>
   </si>
@@ -375,6 +375,30 @@
   </si>
   <si>
     <t>忽视层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aroundEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周身特效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/雷电黄色周身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红方玩家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝方玩家</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -691,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -700,9 +724,10 @@
     <col min="6" max="8" width="81.83203125" customWidth="1"/>
     <col min="9" max="10" width="135.75" customWidth="1"/>
     <col min="11" max="11" width="57.25" customWidth="1"/>
+    <col min="14" max="14" width="31.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -742,8 +767,11 @@
       <c r="M1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -783,8 +811,11 @@
       <c r="M2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -824,8 +855,11 @@
       <c r="M3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>101</v>
       </c>
@@ -866,7 +900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>102</v>
       </c>
@@ -907,7 +941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>103</v>
       </c>
@@ -948,7 +982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>104</v>
       </c>
@@ -989,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>105</v>
       </c>
@@ -1030,7 +1064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>106</v>
       </c>
@@ -1071,7 +1105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>107</v>
       </c>
@@ -1112,7 +1146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>108</v>
       </c>
@@ -1153,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>109</v>
       </c>
@@ -1194,7 +1228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>110</v>
       </c>
@@ -1235,7 +1269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>111</v>
       </c>
@@ -1276,7 +1310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>201</v>
       </c>
@@ -1317,7 +1351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>202</v>
       </c>
@@ -1358,7 +1392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>203</v>
       </c>
@@ -1399,7 +1433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>204</v>
       </c>
@@ -1440,7 +1474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>205</v>
       </c>
@@ -1481,7 +1515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>206</v>
       </c>
@@ -1522,7 +1556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>207</v>
       </c>
@@ -1563,7 +1597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:14">
       <c r="A22">
         <v>1001</v>
       </c>
@@ -1603,8 +1637,11 @@
       <c r="M22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23">
         <v>1002</v>
       </c>
@@ -1644,8 +1681,11 @@
       <c r="M23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24">
         <v>1003</v>
       </c>
@@ -1685,8 +1725,11 @@
       <c r="M24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25">
         <v>1004</v>
       </c>
@@ -1726,8 +1769,11 @@
       <c r="M25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26">
         <v>1005</v>
       </c>
@@ -1767,8 +1813,11 @@
       <c r="M26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27">
         <v>2001</v>
       </c>
@@ -1808,8 +1857,11 @@
       <c r="M27">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28">
         <v>2002</v>
       </c>
@@ -1849,8 +1901,11 @@
       <c r="M28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29">
         <v>2003</v>
       </c>
@@ -1890,8 +1945,11 @@
       <c r="M29">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30">
         <v>2004</v>
       </c>
@@ -1931,8 +1989,11 @@
       <c r="M30">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31">
         <v>2005</v>
       </c>
@@ -1972,8 +2033,11 @@
       <c r="M31">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="N31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32">
         <v>10001</v>
       </c>
@@ -2052,6 +2116,82 @@
         <v>0</v>
       </c>
       <c r="M33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34">
+        <v>30001</v>
+      </c>
+      <c r="B34" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>1000</v>
+      </c>
+      <c r="F34">
+        <v>1000</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35">
+        <v>30002</v>
+      </c>
+      <c r="B35" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>1000</v>
+      </c>
+      <c r="F35">
+        <v>1000</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
         <v>0</v>
       </c>
     </row>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="-120" windowWidth="28840" windowHeight="11930"/>
+    <workbookView xWindow="-10" yWindow="-10" windowWidth="19280" windowHeight="18180"/>
   </bookViews>
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="129">
   <si>
     <t>id</t>
   </si>
@@ -399,6 +399,94 @@
   </si>
   <si>
     <t>蓝方玩家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,17</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,16</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,20</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,23</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9,18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11,26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12,24</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -406,7 +494,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,6 +505,14 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -441,8 +537,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1607,14 +1704,14 @@
       <c r="C22" t="s">
         <v>73</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E22">
         <v>500</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>15</v>
@@ -1651,20 +1748,20 @@
       <c r="C23" t="s">
         <v>76</v>
       </c>
-      <c r="D23">
-        <v>6</v>
+      <c r="D23" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23">
         <v>101</v>
@@ -1695,20 +1792,20 @@
       <c r="C24" t="s">
         <v>79</v>
       </c>
-      <c r="D24">
-        <v>7</v>
+      <c r="D24" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24">
         <v>101</v>
@@ -1739,20 +1836,20 @@
       <c r="C25" t="s">
         <v>82</v>
       </c>
-      <c r="D25">
-        <v>8</v>
+      <c r="D25" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25">
         <v>101</v>
@@ -1783,20 +1880,20 @@
       <c r="C26" t="s">
         <v>85</v>
       </c>
-      <c r="D26">
-        <v>9</v>
+      <c r="D26" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26">
         <v>101</v>
@@ -1827,20 +1924,20 @@
       <c r="C27" t="s">
         <v>88</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27">
+        <v>500</v>
+      </c>
+      <c r="F27">
         <v>10</v>
       </c>
-      <c r="E27">
-        <v>5</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
       <c r="G27">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27">
         <v>101</v>
@@ -1871,20 +1968,20 @@
       <c r="C28" t="s">
         <v>91</v>
       </c>
-      <c r="D28">
-        <v>11</v>
+      <c r="D28" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>101</v>
@@ -1915,20 +2012,20 @@
       <c r="C29" t="s">
         <v>94</v>
       </c>
-      <c r="D29">
-        <v>12</v>
+      <c r="D29" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <v>101</v>
@@ -1959,20 +2056,20 @@
       <c r="C30" t="s">
         <v>97</v>
       </c>
-      <c r="D30">
-        <v>13</v>
+      <c r="D30" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30">
         <v>101</v>
@@ -2003,20 +2100,20 @@
       <c r="C31" t="s">
         <v>100</v>
       </c>
-      <c r="D31">
-        <v>14</v>
+      <c r="D31" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>101</v>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyProject\WorldIsMine\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-10" yWindow="-10" windowWidth="19280" windowHeight="18180"/>
+    <workbookView windowWidth="28800" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="121">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +67,15 @@
     <t>prefab</t>
   </si>
   <si>
+    <t>myLayer</t>
+  </si>
+  <si>
+    <t>ignoreLayer</t>
+  </si>
+  <si>
+    <t>aroundEffect</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -107,6 +121,15 @@
     <t>预制体名字</t>
   </si>
   <si>
+    <t>当前层</t>
+  </si>
+  <si>
+    <t>忽视层</t>
+  </si>
+  <si>
+    <t>周身特效</t>
+  </si>
+  <si>
     <t>刀盾兵</t>
   </si>
   <si>
@@ -125,75 +148,60 @@
     <t>Soldier/Soldier2_1</t>
   </si>
   <si>
-    <t>短锤兵</t>
+    <t>骑兵</t>
+  </si>
+  <si>
+    <t>骑兵(三)</t>
+  </si>
+  <si>
+    <t>Soldier/Soldier11_1</t>
+  </si>
+  <si>
+    <t>枪兵</t>
+  </si>
+  <si>
+    <t>枪兵(三)</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Soldier/Soldier8_1</t>
+  </si>
+  <si>
+    <t>锤兵</t>
   </si>
   <si>
     <t>短锤兵(三)</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>Soldier/Soldier3_1</t>
   </si>
   <si>
-    <t>炮兵</t>
-  </si>
-  <si>
-    <t>炮兵(三)</t>
-  </si>
-  <si>
-    <t>Soldier/Soldier4_1</t>
-  </si>
-  <si>
-    <t>长锤兵</t>
-  </si>
-  <si>
-    <t>长锤兵(三)</t>
-  </si>
-  <si>
-    <t>Soldier/Soldier6_1</t>
-  </si>
-  <si>
-    <t>弩兵</t>
-  </si>
-  <si>
-    <t>弩兵(三)</t>
-  </si>
-  <si>
-    <t>Soldier/Soldier7_1</t>
-  </si>
-  <si>
-    <t>枪兵</t>
-  </si>
-  <si>
-    <t>枪兵(三)</t>
-  </si>
-  <si>
-    <t>Soldier/Soldier8_1</t>
-  </si>
-  <si>
     <t>弩车</t>
   </si>
   <si>
     <t>弩车(三)</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>Soldier/Soldier10_1</t>
   </si>
   <si>
-    <t>骑兵</t>
-  </si>
-  <si>
-    <t>骑兵(三)</t>
-  </si>
-  <si>
-    <t>Soldier/Soldier11_1</t>
-  </si>
-  <si>
     <t>投石车</t>
   </si>
   <si>
     <t>投石车(三)</t>
   </si>
   <si>
+    <t>Soldier/Soldier13_1</t>
+  </si>
+  <si>
     <t>冲车</t>
   </si>
   <si>
@@ -215,18 +223,18 @@
     <t>Soldier/Soldier2_2_qin</t>
   </si>
   <si>
+    <t>骑兵(秦)</t>
+  </si>
+  <si>
+    <t>Soldier/Soldier11_2_qin</t>
+  </si>
+  <si>
     <t>枪兵(秦)</t>
   </si>
   <si>
     <t>Soldier/Soldier8_2_qin</t>
   </si>
   <si>
-    <t>骑兵(秦)</t>
-  </si>
-  <si>
-    <t>Soldier/Soldier11_2_qin</t>
-  </si>
-  <si>
     <t>弩车(秦)</t>
   </si>
   <si>
@@ -251,15 +259,24 @@
     <t>吕布(三)</t>
   </si>
   <si>
+    <t>10001,100007</t>
+  </si>
+  <si>
     <t>Soldier/Hero22_1</t>
   </si>
   <si>
+    <t>Effects/Hero_Foot_Smoke</t>
+  </si>
+  <si>
     <t>刘备</t>
   </si>
   <si>
     <t>刘备(三)</t>
   </si>
   <si>
+    <t>10002,100001</t>
+  </si>
+  <si>
     <t>Soldier/Hero10_1</t>
   </si>
   <si>
@@ -269,6 +286,9 @@
     <t>关羽(三)</t>
   </si>
   <si>
+    <t>10003,100003</t>
+  </si>
+  <si>
     <t>Soldier/Hero11_1</t>
   </si>
   <si>
@@ -278,6 +298,9 @@
     <t>张飞(三)</t>
   </si>
   <si>
+    <t>10004,100002</t>
+  </si>
+  <si>
     <t>Soldier/Hero12_1</t>
   </si>
   <si>
@@ -287,6 +310,9 @@
     <t>赵云(三)</t>
   </si>
   <si>
+    <t>10005,100004</t>
+  </si>
+  <si>
     <t>Soldier/Hero13_1</t>
   </si>
   <si>
@@ -296,6 +322,9 @@
     <t>项羽(秦)</t>
   </si>
   <si>
+    <t>10101,100010</t>
+  </si>
+  <si>
     <t>Soldier/Hero33_1</t>
   </si>
   <si>
@@ -305,6 +334,9 @@
     <t>刘邦(秦)</t>
   </si>
   <si>
+    <t>10102,100011</t>
+  </si>
+  <si>
     <t>Soldier/Hero43_1</t>
   </si>
   <si>
@@ -314,6 +346,9 @@
     <t>韩信(秦)</t>
   </si>
   <si>
+    <t>10103,100009</t>
+  </si>
+  <si>
     <t>Soldier/Hero34_1</t>
   </si>
   <si>
@@ -323,6 +358,9 @@
     <t>樊哙(秦)</t>
   </si>
   <si>
+    <t>10104,100006</t>
+  </si>
+  <si>
     <t>Soldier/Hero26_1</t>
   </si>
   <si>
@@ -332,6 +370,9 @@
     <t>项庄(秦)</t>
   </si>
   <si>
+    <t>10105,100008</t>
+  </si>
+  <si>
     <t>Soldier/Hero38_1</t>
   </si>
   <si>
@@ -350,151 +391,23 @@
     <t>City/Door_qin</t>
   </si>
   <si>
-    <t>5,21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier13_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>myLayer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ignoreLayer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前层</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>忽视层</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aroundEffect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>周身特效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/雷电黄色周身</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>红方玩家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>蓝方玩家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6,15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,17</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,16</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,20</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,23</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9,18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11,26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12,24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,29 +416,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -533,18 +762,308 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -806,22 +1325,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="3" width="18.08203125" customWidth="1"/>
-    <col min="4" max="4" width="19.4140625" customWidth="1"/>
-    <col min="6" max="8" width="81.83203125" customWidth="1"/>
-    <col min="9" max="10" width="135.75" customWidth="1"/>
-    <col min="11" max="11" width="57.25" customWidth="1"/>
-    <col min="14" max="14" width="31.58203125" customWidth="1"/>
+    <col min="1" max="1" width="15.2477876106195" customWidth="1"/>
+    <col min="2" max="3" width="18.0796460176991" customWidth="1"/>
+    <col min="4" max="4" width="19.4159292035398" customWidth="1"/>
+    <col min="6" max="8" width="81.8318584070797" customWidth="1"/>
+    <col min="9" max="10" width="135.752212389381" customWidth="1"/>
+    <col min="11" max="11" width="57.2477876106195" customWidth="1"/>
+    <col min="14" max="14" width="31.5840707964602" customWidth="1"/>
+    <col min="15" max="15" width="8.82300884955752" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -859,101 +1379,101 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>14</v>
       </c>
-      <c r="K2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" t="s">
-        <v>111</v>
-      </c>
-      <c r="M2" t="s">
-        <v>111</v>
-      </c>
       <c r="N2" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L3" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="M3" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="N3" t="s">
-        <v>116</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -961,12 +1481,12 @@
         <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1">
         <v>1</v>
       </c>
       <c r="E4">
@@ -976,10 +1496,10 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H4">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -988,7 +1508,7 @@
         <v>1.5</v>
       </c>
       <c r="K4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -1002,12 +1522,12 @@
         <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5">
+        <v>36</v>
+      </c>
+      <c r="D5" s="1">
         <v>2</v>
       </c>
       <c r="E5">
@@ -1017,10 +1537,10 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1029,7 +1549,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -1043,13 +1563,13 @@
         <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1058,19 +1578,19 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>1.5</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -1084,13 +1604,13 @@
         <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1099,19 +1619,19 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>1.5</v>
       </c>
       <c r="K7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -1125,13 +1645,13 @@
         <v>105</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
+        <v>46</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1140,19 +1660,19 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>1.5</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -1166,13 +1686,13 @@
         <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
+        <v>50</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E9">
         <v>5</v>
@@ -1181,19 +1701,19 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J9">
         <v>1.5</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -1207,13 +1727,13 @@
         <v>107</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -1222,19 +1742,19 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J10">
         <v>1.5</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -1248,13 +1768,13 @@
         <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
+        <v>57</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -1263,10 +1783,10 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>11</v>
@@ -1275,7 +1795,7 @@
         <v>1.5</v>
       </c>
       <c r="K11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -1286,16 +1806,16 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12">
-        <v>109</v>
+        <v>201</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12">
-        <v>3</v>
+        <v>59</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
       </c>
       <c r="E12">
         <v>5</v>
@@ -1304,22 +1824,22 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>1.5</v>
       </c>
       <c r="K12" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -1327,16 +1847,16 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13">
-        <v>22</v>
+        <v>61</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -1345,22 +1865,22 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H13">
+        <v>1.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.5</v>
+      </c>
+      <c r="K13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13">
         <v>2</v>
-      </c>
-      <c r="I13">
-        <v>11</v>
-      </c>
-      <c r="J13">
-        <v>1.5</v>
-      </c>
-      <c r="K13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -1368,16 +1888,16 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
+        <v>63</v>
+      </c>
+      <c r="D14" s="1">
+        <v>3</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -1386,22 +1906,22 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J14">
         <v>1.5</v>
       </c>
       <c r="K14" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -1409,16 +1929,16 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -1427,19 +1947,19 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H15">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15">
         <v>1.5</v>
       </c>
       <c r="K15" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L15">
         <v>2</v>
@@ -1448,18 +1968,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" customFormat="1" spans="1:14">
       <c r="A16">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
+        <v>46</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E16">
         <v>5</v>
@@ -1468,10 +1988,10 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1480,10 +2000,10 @@
         <v>1.5</v>
       </c>
       <c r="K16" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="L16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -1491,16 +2011,16 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
+        <v>67</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -1512,16 +2032,16 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J17">
         <v>1.5</v>
       </c>
       <c r="K17" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L17">
         <v>2</v>
@@ -1532,16 +2052,16 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18">
-        <v>3</v>
+        <v>69</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E18">
         <v>5</v>
@@ -1550,19 +2070,19 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J18">
         <v>1.5</v>
       </c>
       <c r="K18" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="L18">
         <v>2</v>
@@ -1573,16 +2093,16 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
+        <v>71</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -1594,7 +2114,7 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19">
         <v>11</v>
@@ -1603,7 +2123,7 @@
         <v>1.5</v>
       </c>
       <c r="K19" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L19">
         <v>2</v>
@@ -1614,98 +2134,104 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20">
-        <v>206</v>
+        <v>1001</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
+        <v>74</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="J20">
         <v>1.5</v>
       </c>
       <c r="K20" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N20" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21">
-        <v>207</v>
+        <v>1002</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
+        <v>79</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="J21">
         <v>1.5</v>
       </c>
       <c r="K21" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N21" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>107</v>
+        <v>83</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="E22">
         <v>500</v>
@@ -1714,10 +2240,10 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22">
         <v>101</v>
@@ -1726,7 +2252,7 @@
         <v>1.5</v>
       </c>
       <c r="K22" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="L22">
         <v>3</v>
@@ -1735,21 +2261,21 @@
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>120</v>
+        <v>87</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="E23">
         <v>500</v>
@@ -1758,10 +2284,10 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
         <v>101</v>
@@ -1770,7 +2296,7 @@
         <v>1.5</v>
       </c>
       <c r="K23" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="L23">
         <v>3</v>
@@ -1779,21 +2305,21 @@
         <v>1</v>
       </c>
       <c r="N23" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>121</v>
+        <v>91</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="E24">
         <v>500</v>
@@ -1802,10 +2328,10 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24">
         <v>101</v>
@@ -1814,7 +2340,7 @@
         <v>1.5</v>
       </c>
       <c r="K24" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="L24">
         <v>3</v>
@@ -1823,21 +2349,21 @@
         <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25">
-        <v>1004</v>
+        <v>2001</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>122</v>
+        <v>95</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="E25">
         <v>500</v>
@@ -1846,10 +2372,10 @@
         <v>10</v>
       </c>
       <c r="G25">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25">
         <v>101</v>
@@ -1858,30 +2384,30 @@
         <v>1.5</v>
       </c>
       <c r="K25" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N25" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26">
-        <v>1005</v>
+        <v>2002</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>125</v>
+        <v>99</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="E26">
         <v>500</v>
@@ -1890,10 +2416,10 @@
         <v>10</v>
       </c>
       <c r="G26">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26">
         <v>101</v>
@@ -1902,30 +2428,30 @@
         <v>1.5</v>
       </c>
       <c r="K26" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="L26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>126</v>
+        <v>103</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="E27">
         <v>500</v>
@@ -1934,10 +2460,10 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27">
         <v>101</v>
@@ -1946,7 +2472,7 @@
         <v>1.5</v>
       </c>
       <c r="K27" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="L27">
         <v>4</v>
@@ -1955,21 +2481,21 @@
         <v>2</v>
       </c>
       <c r="N27" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>127</v>
+        <v>107</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="E28">
         <v>500</v>
@@ -1978,10 +2504,10 @@
         <v>10</v>
       </c>
       <c r="G28">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>101</v>
@@ -1990,7 +2516,7 @@
         <v>1.5</v>
       </c>
       <c r="K28" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="L28">
         <v>4</v>
@@ -1999,21 +2525,21 @@
         <v>2</v>
       </c>
       <c r="N28" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>128</v>
+        <v>111</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="E29">
         <v>500</v>
@@ -2022,10 +2548,10 @@
         <v>10</v>
       </c>
       <c r="G29">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29">
         <v>101</v>
@@ -2034,7 +2560,7 @@
         <v>1.5</v>
       </c>
       <c r="K29" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="L29">
         <v>4</v>
@@ -2043,112 +2569,106 @@
         <v>2</v>
       </c>
       <c r="N29" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30">
-        <v>2004</v>
+        <v>10001</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="F30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="J30">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="L30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>2</v>
-      </c>
-      <c r="N30" t="s">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31">
-        <v>2005</v>
+        <v>20001</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="J31">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>2</v>
-      </c>
-      <c r="N31" t="s">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32">
-        <v>10001</v>
+        <v>30001</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
-      </c>
-      <c r="D32">
+        <v>119</v>
+      </c>
+      <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2160,13 +2680,10 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <v>1</v>
-      </c>
-      <c r="K32" t="s">
-        <v>104</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2177,19 +2694,19 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33">
-        <v>20001</v>
+        <v>30002</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33">
+        <v>120</v>
+      </c>
+      <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -2201,14 +2718,11 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
-      <c r="K33" t="s">
-        <v>106</v>
-      </c>
       <c r="L33">
         <v>0</v>
       </c>
@@ -2216,84 +2730,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
-      <c r="A34">
-        <v>30001</v>
-      </c>
-      <c r="B34" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" t="s">
-        <v>118</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>1000</v>
-      </c>
-      <c r="F34">
-        <v>1000</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35">
-        <v>30002</v>
-      </c>
-      <c r="B35" t="s">
-        <v>119</v>
-      </c>
-      <c r="C35" t="s">
-        <v>119</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>1000</v>
-      </c>
-      <c r="F35">
-        <v>1000</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="123">
   <si>
     <t>id</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Soldier/Hero22_1</t>
   </si>
   <si>
+    <t>1,5</t>
+  </si>
+  <si>
     <t>Effects/Hero_Foot_Smoke</t>
   </si>
   <si>
@@ -326,6 +329,9 @@
   </si>
   <si>
     <t>Soldier/Hero33_1</t>
+  </si>
+  <si>
+    <t>2,6</t>
   </si>
   <si>
     <t>刘邦</t>
@@ -1426,7 +1432,7 @@
         <v>14</v>
       </c>
       <c r="M2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N2" t="s">
         <v>15</v>
@@ -1514,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1552,7 +1558,7 @@
         <v>37</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -1596,7 +1602,7 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1637,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1678,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1719,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1760,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1801,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1842,10 +1848,10 @@
         <v>2</v>
       </c>
       <c r="M12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1" spans="1:14">
       <c r="A13">
         <v>202</v>
       </c>
@@ -1880,7 +1886,7 @@
         <v>62</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -1924,7 +1930,7 @@
         <v>2</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1965,7 +1971,7 @@
         <v>2</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:14">
@@ -2003,10 +2009,10 @@
         <v>48</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -2047,7 +2053,7 @@
         <v>2</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -2088,7 +2094,7 @@
         <v>2</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -2129,7 +2135,7 @@
         <v>2</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -2169,11 +2175,11 @@
       <c r="L20">
         <v>3</v>
       </c>
-      <c r="M20">
-        <v>1</v>
+      <c r="M20" t="s">
+        <v>77</v>
       </c>
       <c r="N20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -2181,13 +2187,13 @@
         <v>1002</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>500</v>
@@ -2208,16 +2214,16 @@
         <v>1.5</v>
       </c>
       <c r="K21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L21">
         <v>3</v>
       </c>
-      <c r="M21">
-        <v>1</v>
+      <c r="M21" t="s">
+        <v>77</v>
       </c>
       <c r="N21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -2225,13 +2231,13 @@
         <v>1003</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22">
         <v>500</v>
@@ -2252,16 +2258,16 @@
         <v>1.5</v>
       </c>
       <c r="K22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L22">
         <v>3</v>
       </c>
-      <c r="M22">
-        <v>1</v>
+      <c r="M22" t="s">
+        <v>77</v>
       </c>
       <c r="N22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -2269,13 +2275,13 @@
         <v>1004</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23">
         <v>500</v>
@@ -2296,16 +2302,16 @@
         <v>1.5</v>
       </c>
       <c r="K23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L23">
         <v>3</v>
       </c>
-      <c r="M23">
-        <v>1</v>
+      <c r="M23" t="s">
+        <v>77</v>
       </c>
       <c r="N23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -2313,13 +2319,13 @@
         <v>1005</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24">
         <v>500</v>
@@ -2340,16 +2346,16 @@
         <v>1.5</v>
       </c>
       <c r="K24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L24">
         <v>3</v>
       </c>
-      <c r="M24">
-        <v>1</v>
+      <c r="M24" t="s">
+        <v>77</v>
       </c>
       <c r="N24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -2357,13 +2363,13 @@
         <v>2001</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E25">
         <v>500</v>
@@ -2384,16 +2390,16 @@
         <v>1.5</v>
       </c>
       <c r="K25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L25">
         <v>4</v>
       </c>
-      <c r="M25">
-        <v>2</v>
+      <c r="M25" t="s">
+        <v>99</v>
       </c>
       <c r="N25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -2401,13 +2407,13 @@
         <v>2002</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E26">
         <v>500</v>
@@ -2428,16 +2434,16 @@
         <v>1.5</v>
       </c>
       <c r="K26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L26">
         <v>4</v>
       </c>
-      <c r="M26">
-        <v>2</v>
+      <c r="M26" t="s">
+        <v>99</v>
       </c>
       <c r="N26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2445,13 +2451,13 @@
         <v>2003</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E27">
         <v>500</v>
@@ -2472,16 +2478,16 @@
         <v>1.5</v>
       </c>
       <c r="K27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L27">
         <v>4</v>
       </c>
-      <c r="M27">
-        <v>2</v>
+      <c r="M27" t="s">
+        <v>99</v>
       </c>
       <c r="N27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2489,13 +2495,13 @@
         <v>2004</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E28">
         <v>500</v>
@@ -2516,16 +2522,16 @@
         <v>1.5</v>
       </c>
       <c r="K28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L28">
         <v>4</v>
       </c>
-      <c r="M28">
-        <v>2</v>
+      <c r="M28" t="s">
+        <v>99</v>
       </c>
       <c r="N28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -2533,13 +2539,13 @@
         <v>2005</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E29">
         <v>500</v>
@@ -2560,16 +2566,16 @@
         <v>1.5</v>
       </c>
       <c r="K29" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L29">
         <v>4</v>
       </c>
-      <c r="M29">
-        <v>2</v>
+      <c r="M29" t="s">
+        <v>99</v>
       </c>
       <c r="N29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2577,10 +2583,10 @@
         <v>10001</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -2604,13 +2610,16 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
         <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2618,10 +2627,10 @@
         <v>20001</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
@@ -2645,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2659,10 +2668,10 @@
         <v>30001</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
@@ -2697,10 +2706,10 @@
         <v>30002</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11655"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
@@ -235,6 +235,9 @@
     <t>Soldier/Soldier8_2_qin</t>
   </si>
   <si>
+    <t>Soldier/Soldier3_2_qin</t>
+  </si>
+  <si>
     <t>弩车(秦)</t>
   </si>
   <si>
@@ -388,13 +391,10 @@
     <t>城门(三)</t>
   </si>
   <si>
-    <t>City/Door</t>
+    <t>Soldier/CityDoor</t>
   </si>
   <si>
     <t>城门(秦)</t>
-  </si>
-  <si>
-    <t>City/Door_qin</t>
   </si>
   <si>
     <t>红方玩家</t>
@@ -2006,7 +2006,7 @@
         <v>1.5</v>
       </c>
       <c r="K16" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="L16">
         <v>2</v>
@@ -2023,7 +2023,7 @@
         <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>51</v>
@@ -2047,7 +2047,7 @@
         <v>1.5</v>
       </c>
       <c r="K17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L17">
         <v>2</v>
@@ -2064,7 +2064,7 @@
         <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>51</v>
@@ -2088,7 +2088,7 @@
         <v>1.5</v>
       </c>
       <c r="K18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L18">
         <v>2</v>
@@ -2105,7 +2105,7 @@
         <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>51</v>
@@ -2129,7 +2129,7 @@
         <v>1.5</v>
       </c>
       <c r="K19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L19">
         <v>2</v>
@@ -2143,13 +2143,13 @@
         <v>1001</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E20">
         <v>500</v>
@@ -2170,16 +2170,16 @@
         <v>1.5</v>
       </c>
       <c r="K20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L20">
         <v>3</v>
       </c>
       <c r="M20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -2187,13 +2187,13 @@
         <v>1002</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21">
         <v>500</v>
@@ -2214,16 +2214,16 @@
         <v>1.5</v>
       </c>
       <c r="K21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L21">
         <v>3</v>
       </c>
       <c r="M21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -2231,13 +2231,13 @@
         <v>1003</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E22">
         <v>500</v>
@@ -2258,16 +2258,16 @@
         <v>1.5</v>
       </c>
       <c r="K22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L22">
         <v>3</v>
       </c>
       <c r="M22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -2275,13 +2275,13 @@
         <v>1004</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E23">
         <v>500</v>
@@ -2302,16 +2302,16 @@
         <v>1.5</v>
       </c>
       <c r="K23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L23">
         <v>3</v>
       </c>
       <c r="M23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -2319,13 +2319,13 @@
         <v>1005</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E24">
         <v>500</v>
@@ -2346,16 +2346,16 @@
         <v>1.5</v>
       </c>
       <c r="K24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L24">
         <v>3</v>
       </c>
       <c r="M24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -2363,13 +2363,13 @@
         <v>2001</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E25">
         <v>500</v>
@@ -2390,16 +2390,16 @@
         <v>1.5</v>
       </c>
       <c r="K25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L25">
         <v>4</v>
       </c>
       <c r="M25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -2407,13 +2407,13 @@
         <v>2002</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E26">
         <v>500</v>
@@ -2434,16 +2434,16 @@
         <v>1.5</v>
       </c>
       <c r="K26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L26">
         <v>4</v>
       </c>
       <c r="M26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2451,13 +2451,13 @@
         <v>2003</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E27">
         <v>500</v>
@@ -2478,16 +2478,16 @@
         <v>1.5</v>
       </c>
       <c r="K27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L27">
         <v>4</v>
       </c>
       <c r="M27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2495,13 +2495,13 @@
         <v>2004</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E28">
         <v>500</v>
@@ -2522,16 +2522,16 @@
         <v>1.5</v>
       </c>
       <c r="K28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L28">
         <v>4</v>
       </c>
       <c r="M28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -2539,13 +2539,13 @@
         <v>2005</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E29">
         <v>500</v>
@@ -2566,16 +2566,16 @@
         <v>1.5</v>
       </c>
       <c r="K29" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L29">
         <v>4</v>
       </c>
       <c r="M29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2583,10 +2583,10 @@
         <v>10001</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -2610,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2627,10 +2627,10 @@
         <v>20001</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L31">
         <v>0</v>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="134">
   <si>
     <t>id</t>
   </si>
@@ -322,6 +322,24 @@
     <t>Soldier/Hero13_1</t>
   </si>
   <si>
+    <t>马超</t>
+  </si>
+  <si>
+    <t>黄忠</t>
+  </si>
+  <si>
+    <t>诸葛亮</t>
+  </si>
+  <si>
+    <t>魏延</t>
+  </si>
+  <si>
+    <t>夏侯惇</t>
+  </si>
+  <si>
+    <t>曹操</t>
+  </si>
+  <si>
     <t>项羽</t>
   </si>
   <si>
@@ -383,6 +401,21 @@
   </si>
   <si>
     <t>Soldier/Hero38_1</t>
+  </si>
+  <si>
+    <t>孙膑</t>
+  </si>
+  <si>
+    <t>廉颇</t>
+  </si>
+  <si>
+    <t>卫青</t>
+  </si>
+  <si>
+    <t>霍去病</t>
+  </si>
+  <si>
+    <t>李广</t>
   </si>
   <si>
     <t>城门</t>
@@ -1337,17 +1370,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
+  <dimension ref="A1:N43"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.2477876106195" customWidth="1"/>
-    <col min="2" max="3" width="18.0796460176991" customWidth="1"/>
-    <col min="4" max="4" width="19.4159292035398" customWidth="1"/>
-    <col min="6" max="8" width="81.8318584070797" customWidth="1"/>
-    <col min="9" max="10" width="135.752212389381" customWidth="1"/>
-    <col min="11" max="11" width="57.2477876106195" customWidth="1"/>
-    <col min="14" max="14" width="31.5840707964602" customWidth="1"/>
-    <col min="15" max="15" width="8.82300884955752" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="3" width="18.0833333333333" customWidth="1"/>
+    <col min="4" max="4" width="19.4166666666667" customWidth="1"/>
+    <col min="6" max="8" width="81.8333333333333" customWidth="1"/>
+    <col min="9" max="10" width="135.75" customWidth="1"/>
+    <col min="11" max="11" width="57.25" customWidth="1"/>
+    <col min="14" max="14" width="31.5833333333333" customWidth="1"/>
+    <col min="15" max="15" width="8.825" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1851,7 +1884,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" ht="14" customHeight="1" spans="1:14">
+    <row r="13" customHeight="1" spans="1:14">
       <c r="A13">
         <v>202</v>
       </c>
@@ -2358,18 +2391,18 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" customFormat="1" spans="1:14">
       <c r="A25">
-        <v>2001</v>
+        <v>1006</v>
       </c>
       <c r="B25" t="s">
         <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E25">
         <v>500</v>
@@ -2390,30 +2423,30 @@
         <v>1.5</v>
       </c>
       <c r="K25" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M25" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="N25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" customFormat="1" spans="1:14">
       <c r="A26">
-        <v>2002</v>
+        <v>1007</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E26">
         <v>500</v>
@@ -2434,30 +2467,30 @@
         <v>1.5</v>
       </c>
       <c r="K26" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="L26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M26" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="N26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" customFormat="1" spans="1:14">
       <c r="A27">
-        <v>2003</v>
+        <v>1008</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E27">
         <v>500</v>
@@ -2478,30 +2511,30 @@
         <v>1.5</v>
       </c>
       <c r="K27" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M27" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="N27" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" customFormat="1" spans="1:14">
       <c r="A28">
-        <v>2004</v>
+        <v>1009</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="E28">
         <v>500</v>
@@ -2522,30 +2555,30 @@
         <v>1.5</v>
       </c>
       <c r="K28" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="L28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="N28" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" customFormat="1" spans="1:14">
       <c r="A29">
-        <v>2005</v>
+        <v>1010</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E29">
         <v>500</v>
@@ -2566,13 +2599,13 @@
         <v>1.5</v>
       </c>
       <c r="K29" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M29" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="N29" t="s">
         <v>79</v>
@@ -2580,43 +2613,43 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30">
-        <v>10001</v>
+        <v>2001</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0</v>
+        <v>103</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="E30">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30">
-        <v>1001</v>
+        <v>101</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K30" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="M30" t="s">
+        <v>106</v>
       </c>
       <c r="N30" t="s">
         <v>79</v>
@@ -2624,118 +2657,558 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31">
-        <v>20001</v>
+        <v>2002</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="E31">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>1001</v>
+        <v>101</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K31" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="M31" t="s">
+        <v>106</v>
+      </c>
+      <c r="N31" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32">
+        <v>2003</v>
+      </c>
+      <c r="B32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32">
+        <v>500</v>
+      </c>
+      <c r="F32">
+        <v>10</v>
+      </c>
+      <c r="G32">
+        <v>30</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32">
+        <v>101</v>
+      </c>
+      <c r="J32">
+        <v>1.5</v>
+      </c>
+      <c r="K32" t="s">
+        <v>114</v>
+      </c>
+      <c r="L32">
+        <v>4</v>
+      </c>
+      <c r="M32" t="s">
+        <v>106</v>
+      </c>
+      <c r="N32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33">
+        <v>2004</v>
+      </c>
+      <c r="B33" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33">
+        <v>500</v>
+      </c>
+      <c r="F33">
+        <v>10</v>
+      </c>
+      <c r="G33">
+        <v>30</v>
+      </c>
+      <c r="H33">
+        <v>3</v>
+      </c>
+      <c r="I33">
+        <v>101</v>
+      </c>
+      <c r="J33">
+        <v>1.5</v>
+      </c>
+      <c r="K33" t="s">
+        <v>118</v>
+      </c>
+      <c r="L33">
+        <v>4</v>
+      </c>
+      <c r="M33" t="s">
+        <v>106</v>
+      </c>
+      <c r="N33" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34">
+        <v>2005</v>
+      </c>
+      <c r="B34" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34">
+        <v>500</v>
+      </c>
+      <c r="F34">
+        <v>10</v>
+      </c>
+      <c r="G34">
+        <v>30</v>
+      </c>
+      <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="I34">
+        <v>101</v>
+      </c>
+      <c r="J34">
+        <v>1.5</v>
+      </c>
+      <c r="K34" t="s">
+        <v>122</v>
+      </c>
+      <c r="L34">
+        <v>4</v>
+      </c>
+      <c r="M34" t="s">
+        <v>106</v>
+      </c>
+      <c r="N34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:14">
+      <c r="A35">
+        <v>2006</v>
+      </c>
+      <c r="B35" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35">
+        <v>500</v>
+      </c>
+      <c r="F35">
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <v>30</v>
+      </c>
+      <c r="H35">
+        <v>3</v>
+      </c>
+      <c r="I35">
+        <v>101</v>
+      </c>
+      <c r="J35">
+        <v>1.5</v>
+      </c>
+      <c r="K35" t="s">
+        <v>122</v>
+      </c>
+      <c r="L35">
+        <v>4</v>
+      </c>
+      <c r="M35" t="s">
+        <v>106</v>
+      </c>
+      <c r="N35" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:14">
+      <c r="A36">
+        <v>2007</v>
+      </c>
+      <c r="B36" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36">
+        <v>500</v>
+      </c>
+      <c r="F36">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>30</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+      <c r="I36">
+        <v>101</v>
+      </c>
+      <c r="J36">
+        <v>1.5</v>
+      </c>
+      <c r="K36" t="s">
+        <v>122</v>
+      </c>
+      <c r="L36">
+        <v>4</v>
+      </c>
+      <c r="M36" t="s">
+        <v>106</v>
+      </c>
+      <c r="N36" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:14">
+      <c r="A37">
+        <v>2008</v>
+      </c>
+      <c r="B37" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37">
+        <v>500</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>30</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37">
+        <v>101</v>
+      </c>
+      <c r="J37">
+        <v>1.5</v>
+      </c>
+      <c r="K37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L37">
+        <v>4</v>
+      </c>
+      <c r="M37" t="s">
+        <v>106</v>
+      </c>
+      <c r="N37" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:14">
+      <c r="A38">
+        <v>2009</v>
+      </c>
+      <c r="B38" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38">
+        <v>500</v>
+      </c>
+      <c r="F38">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>30</v>
+      </c>
+      <c r="H38">
+        <v>3</v>
+      </c>
+      <c r="I38">
+        <v>101</v>
+      </c>
+      <c r="J38">
+        <v>1.5</v>
+      </c>
+      <c r="K38" t="s">
+        <v>122</v>
+      </c>
+      <c r="L38">
+        <v>4</v>
+      </c>
+      <c r="M38" t="s">
+        <v>106</v>
+      </c>
+      <c r="N38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:14">
+      <c r="A39">
+        <v>2010</v>
+      </c>
+      <c r="B39" t="s">
+        <v>127</v>
+      </c>
+      <c r="C39" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39">
+        <v>500</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>30</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39">
+        <v>101</v>
+      </c>
+      <c r="J39">
+        <v>1.5</v>
+      </c>
+      <c r="K39" t="s">
+        <v>122</v>
+      </c>
+      <c r="L39">
+        <v>4</v>
+      </c>
+      <c r="M39" t="s">
+        <v>106</v>
+      </c>
+      <c r="N39" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40">
+        <v>10001</v>
+      </c>
+      <c r="B40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>5000</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>1001</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40" t="s">
+        <v>130</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41">
+        <v>20001</v>
+      </c>
+      <c r="B41" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>5000</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>1001</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41" t="s">
+        <v>130</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42">
         <v>30001</v>
       </c>
-      <c r="B32" t="s">
-        <v>121</v>
-      </c>
-      <c r="C32" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" s="1">
+      <c r="B42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="1">
         <v>0</v>
       </c>
-      <c r="E32">
+      <c r="E42">
         <v>1000</v>
       </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32">
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
         <v>0</v>
       </c>
-      <c r="H32">
+      <c r="H42">
         <v>0</v>
       </c>
-      <c r="I32">
+      <c r="I42">
         <v>0</v>
       </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-      <c r="L32">
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="L42">
         <v>0</v>
       </c>
-      <c r="M32">
+      <c r="M42">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
-      <c r="A33">
+    <row r="43" spans="1:14">
+      <c r="A43">
         <v>30002</v>
       </c>
-      <c r="B33" t="s">
-        <v>122</v>
-      </c>
-      <c r="C33" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" s="1">
+      <c r="B43" t="s">
+        <v>133</v>
+      </c>
+      <c r="C43" t="s">
+        <v>133</v>
+      </c>
+      <c r="D43" s="1">
         <v>0</v>
       </c>
-      <c r="E33">
+      <c r="E43">
         <v>1000</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33">
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
         <v>0</v>
       </c>
-      <c r="H33">
+      <c r="H43">
         <v>0</v>
       </c>
-      <c r="I33">
+      <c r="I43">
         <v>0</v>
       </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
-      <c r="L33">
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="L43">
         <v>0</v>
       </c>
-      <c r="M33">
+      <c r="M43">
         <v>0</v>
       </c>
     </row>
